--- a/Assets/Data/Dungeon0020.xlsx
+++ b/Assets/Data/Dungeon0020.xlsx
@@ -55,9 +55,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -76,9 +76,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -92,7 +91,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -100,6 +99,66 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -114,70 +173,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -190,23 +190,15 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,6 +207,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -229,7 +229,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -241,19 +271,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -265,13 +295,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -289,13 +361,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -307,37 +373,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -349,67 +385,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,6 +424,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -434,6 +449,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -456,8 +480,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -467,41 +491,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -520,6 +509,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -528,145 +528,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Dungeon0020.xlsx
+++ b/Assets/Data/Dungeon0020.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="12">
   <si>
     <t>Id</t>
   </si>
@@ -47,6 +47,9 @@
     <t>Out</t>
   </si>
   <si>
+    <t>Dr</t>
+  </si>
+  <si>
     <t>Ev</t>
   </si>
 </sst>
@@ -55,9 +58,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -76,6 +79,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -90,46 +116,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -142,16 +131,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -174,23 +170,15 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -206,7 +194,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -214,7 +202,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -229,19 +232,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -259,25 +382,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -289,127 +406,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -423,16 +426,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -449,15 +452,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -489,23 +483,32 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -528,145 +531,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1833,7 +1836,7 @@
         <v>8</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1" t="s">

--- a/Assets/Data/Dungeon0020.xlsx
+++ b/Assets/Data/Dungeon0020.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="13">
   <si>
     <t>Id</t>
   </si>
@@ -44,6 +44,9 @@
     <t>■</t>
   </si>
   <si>
+    <t>Mv</t>
+  </si>
+  <si>
     <t>Out</t>
   </si>
   <si>
@@ -58,10 +61,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -79,17 +82,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -97,20 +91,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -125,39 +105,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -177,6 +127,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -185,8 +172,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -208,16 +203,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,7 +235,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -244,13 +259,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -262,19 +277,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -292,7 +295,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -304,7 +361,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -316,67 +373,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -388,7 +391,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -400,19 +403,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -423,21 +426,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -452,6 +440,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -483,32 +495,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -531,145 +534,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1186,7 +1189,7 @@
         <v>8</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>8</v>
@@ -1246,7 +1249,7 @@
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
@@ -1258,9 +1261,7 @@
       <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,9 +1330,7 @@
       <c r="H4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1827,7 +1826,7 @@
         <v>8</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>8</v>
@@ -1836,7 +1835,7 @@
         <v>8</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1" t="s">

--- a/Assets/Data/Dungeon0020.xlsx
+++ b/Assets/Data/Dungeon0020.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="13">
   <si>
     <t>Id</t>
   </si>
@@ -61,10 +61,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -82,6 +82,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -89,8 +105,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -105,7 +145,35 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -120,83 +188,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -212,7 +204,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,11 +212,19 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -232,6 +232,96 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -241,19 +331,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -265,31 +355,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -301,43 +367,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -349,6 +385,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -361,61 +403,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -426,36 +426,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -485,8 +455,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -496,7 +468,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -516,13 +488,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -534,145 +534,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1194,27 +1194,13 @@
       <c r="J2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
@@ -1265,27 +1251,13 @@
       <c r="J3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
@@ -1334,27 +1306,13 @@
       <c r="J4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
@@ -1405,27 +1363,13 @@
       <c r="J5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
@@ -1478,27 +1422,13 @@
       <c r="J6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
@@ -1551,27 +1481,13 @@
       <c r="J7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
@@ -1642,9 +1558,7 @@
       <c r="P8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
@@ -1707,9 +1621,7 @@
       <c r="P9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
@@ -1774,9 +1686,7 @@
       <c r="P10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
@@ -1845,9 +1755,7 @@
       <c r="P11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q11" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
@@ -1912,9 +1820,7 @@
       <c r="P12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
@@ -1971,9 +1877,7 @@
       <c r="P13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q13" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
@@ -2040,9 +1944,7 @@
       <c r="P14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
@@ -2072,21 +1974,11 @@
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
         <v>8</v>
       </c>
@@ -2101,9 +1993,7 @@
       <c r="P15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -2133,21 +2023,11 @@
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
       <c r="G16" s="1" t="s">
         <v>8</v>
       </c>
@@ -2178,9 +2058,7 @@
       <c r="P16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q16" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
@@ -2210,54 +2088,22 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>

--- a/Assets/Data/Dungeon0020.xlsx
+++ b/Assets/Data/Dungeon0020.xlsx
@@ -53,7 +53,7 @@
     <t>Dr</t>
   </si>
   <si>
-    <t>Ev</t>
+    <t>Mg</t>
   </si>
 </sst>
 </file>
@@ -61,9 +61,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -82,40 +82,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -123,22 +91,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -158,6 +110,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -165,23 +125,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -195,8 +149,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -210,6 +187,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -219,10 +219,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -235,13 +235,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -253,13 +337,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -271,13 +355,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -289,67 +391,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -361,19 +403,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,37 +415,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -429,11 +429,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -455,10 +461,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -467,8 +471,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -489,16 +493,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -512,17 +516,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -534,145 +534,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Dungeon0020.xlsx
+++ b/Assets/Data/Dungeon0020.xlsx
@@ -1,21 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8A946A-8BBC-40E6-B5F6-44B5707BD908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
     <sheet name="B1F" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525" concurrentCalc="0"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="13">
   <si>
     <t>Id</t>
   </si>
@@ -59,14 +76,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,345 +93,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -428,251 +116,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -687,61 +133,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
-    <cellStyle name="入力" xfId="2" builtinId="20"/>
-    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
-    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
-    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
-    <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
-    <cellStyle name="良い" xfId="13" builtinId="26"/>
-    <cellStyle name="警告文" xfId="14" builtinId="11"/>
-    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
-    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
-    <cellStyle name="説明文" xfId="17" builtinId="53"/>
-    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
-    <cellStyle name="出力" xfId="19" builtinId="21"/>
-    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
-    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
-    <cellStyle name="計算" xfId="22" builtinId="22"/>
-    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
-    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
-    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
-    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
-    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
-    <cellStyle name="集計" xfId="28" builtinId="25"/>
-    <cellStyle name="悪い" xfId="29" builtinId="27"/>
-    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
-    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
-    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
-    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
-    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
-    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
-    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
-    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
-    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
-    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
-    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
-    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
-    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
-    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
-    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
-    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
-    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1028,16 +430,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="1" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1063,7 +465,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>20</v>
       </c>
@@ -1090,27 +492,26 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AO41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.27272727272727" customWidth="1"/>
-    <col min="2" max="2" width="2.27272727272727" customWidth="1"/>
-    <col min="3" max="3" width="3.54545454545455" customWidth="1"/>
-    <col min="4" max="8" width="2.27272727272727" customWidth="1"/>
-    <col min="9" max="10" width="3.54545454545455" customWidth="1"/>
-    <col min="11" max="40" width="3.27272727272727" customWidth="1"/>
-    <col min="41" max="41" width="2.81818181818182" customWidth="1"/>
+    <col min="1" max="1" width="3.26953125" customWidth="1"/>
+    <col min="2" max="2" width="2.26953125" customWidth="1"/>
+    <col min="3" max="3" width="3.54296875" customWidth="1"/>
+    <col min="4" max="8" width="2.26953125" customWidth="1"/>
+    <col min="9" max="10" width="3.54296875" customWidth="1"/>
+    <col min="11" max="40" width="3.26953125" customWidth="1"/>
+    <col min="41" max="41" width="2.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A1" s="1">
         <v>0</v>
       </c>
@@ -1163,7 +564,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:41">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1226,7 +627,7 @@
       <c r="AN2" s="1"/>
       <c r="AO2" s="1"/>
     </row>
-    <row r="3" spans="1:41">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1237,7 +638,9 @@
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>8</v>
       </c>
@@ -1283,7 +686,7 @@
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
     </row>
-    <row r="4" spans="1:41">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1291,8 +694,12 @@
         <v>8</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1338,7 +745,7 @@
       <c r="AN4" s="1"/>
       <c r="AO4" s="1"/>
     </row>
-    <row r="5" spans="1:41">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1346,7 +753,9 @@
         <v>8</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1395,7 +804,7 @@
       <c r="AN5" s="1"/>
       <c r="AO5" s="1"/>
     </row>
-    <row r="6" spans="1:41">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1454,7 +863,7 @@
       <c r="AN6" s="1"/>
       <c r="AO6" s="1"/>
     </row>
-    <row r="7" spans="1:41">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1513,7 +922,7 @@
       <c r="AN7" s="1"/>
       <c r="AO7" s="1"/>
     </row>
-    <row r="8" spans="1:41">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1584,7 +993,7 @@
       <c r="AN8" s="1"/>
       <c r="AO8" s="1"/>
     </row>
-    <row r="9" spans="1:41">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1647,7 +1056,7 @@
       <c r="AN9" s="1"/>
       <c r="AO9" s="1"/>
     </row>
-    <row r="10" spans="1:41">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1712,7 +1121,7 @@
       <c r="AN10" s="1"/>
       <c r="AO10" s="1"/>
     </row>
-    <row r="11" spans="1:41">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1781,7 +1190,7 @@
       <c r="AN11" s="1"/>
       <c r="AO11" s="1"/>
     </row>
-    <row r="12" spans="1:41">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1801,9 +1210,13 @@
       <c r="G12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="1"/>
+      <c r="H12" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="K12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1846,7 +1259,7 @@
       <c r="AN12" s="1"/>
       <c r="AO12" s="1"/>
     </row>
-    <row r="13" spans="1:41">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1903,7 +1316,7 @@
       <c r="AN13" s="1"/>
       <c r="AO13" s="1"/>
     </row>
-    <row r="14" spans="1:41">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1926,7 +1339,9 @@
         <v>8</v>
       </c>
       <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="I14" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1" t="s">
         <v>8</v>
@@ -1970,7 +1385,7 @@
       <c r="AN14" s="1"/>
       <c r="AO14" s="1"/>
     </row>
-    <row r="15" spans="1:41">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2019,7 +1434,7 @@
       <c r="AN15" s="1"/>
       <c r="AO15" s="1"/>
     </row>
-    <row r="16" spans="1:41">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2084,7 +1499,7 @@
       <c r="AN16" s="1"/>
       <c r="AO16" s="1"/>
     </row>
-    <row r="17" spans="1:41">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2129,7 +1544,7 @@
       <c r="AN17" s="1"/>
       <c r="AO17" s="1"/>
     </row>
-    <row r="18" spans="2:41">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -2171,7 +1586,7 @@
       <c r="AN18" s="1"/>
       <c r="AO18" s="1"/>
     </row>
-    <row r="19" spans="2:41">
+    <row r="19" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -2213,7 +1628,7 @@
       <c r="AN19" s="1"/>
       <c r="AO19" s="1"/>
     </row>
-    <row r="20" spans="2:41">
+    <row r="20" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -2255,7 +1670,7 @@
       <c r="AN20" s="1"/>
       <c r="AO20" s="1"/>
     </row>
-    <row r="21" spans="2:41">
+    <row r="21" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -2297,7 +1712,7 @@
       <c r="AN21" s="1"/>
       <c r="AO21" s="1"/>
     </row>
-    <row r="22" spans="2:41">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -2339,7 +1754,7 @@
       <c r="AN22" s="1"/>
       <c r="AO22" s="1"/>
     </row>
-    <row r="23" spans="2:41">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -2381,7 +1796,7 @@
       <c r="AN23" s="1"/>
       <c r="AO23" s="1"/>
     </row>
-    <row r="24" spans="2:41">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -2423,7 +1838,7 @@
       <c r="AN24" s="1"/>
       <c r="AO24" s="1"/>
     </row>
-    <row r="25" spans="2:41">
+    <row r="25" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -2465,7 +1880,7 @@
       <c r="AN25" s="1"/>
       <c r="AO25" s="1"/>
     </row>
-    <row r="26" spans="2:41">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -2507,7 +1922,7 @@
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
     </row>
-    <row r="27" spans="2:41">
+    <row r="27" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -2549,7 +1964,7 @@
       <c r="AN27" s="1"/>
       <c r="AO27" s="1"/>
     </row>
-    <row r="28" spans="2:41">
+    <row r="28" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -2591,7 +2006,7 @@
       <c r="AN28" s="1"/>
       <c r="AO28" s="1"/>
     </row>
-    <row r="29" spans="2:41">
+    <row r="29" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -2633,7 +2048,7 @@
       <c r="AN29" s="1"/>
       <c r="AO29" s="1"/>
     </row>
-    <row r="30" spans="2:41">
+    <row r="30" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -2675,7 +2090,7 @@
       <c r="AN30" s="1"/>
       <c r="AO30" s="1"/>
     </row>
-    <row r="31" spans="2:41">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -2717,7 +2132,7 @@
       <c r="AN31" s="1"/>
       <c r="AO31" s="1"/>
     </row>
-    <row r="32" spans="2:41">
+    <row r="32" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -2759,7 +2174,7 @@
       <c r="AN32" s="1"/>
       <c r="AO32" s="1"/>
     </row>
-    <row r="33" spans="2:41">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -2801,7 +2216,7 @@
       <c r="AN33" s="1"/>
       <c r="AO33" s="1"/>
     </row>
-    <row r="34" spans="2:41">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -2843,7 +2258,7 @@
       <c r="AN34" s="1"/>
       <c r="AO34" s="1"/>
     </row>
-    <row r="35" spans="2:41">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -2885,7 +2300,7 @@
       <c r="AN35" s="1"/>
       <c r="AO35" s="1"/>
     </row>
-    <row r="36" spans="2:41">
+    <row r="36" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -2927,7 +2342,7 @@
       <c r="AN36" s="1"/>
       <c r="AO36" s="1"/>
     </row>
-    <row r="37" spans="2:41">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -2969,7 +2384,7 @@
       <c r="AN37" s="1"/>
       <c r="AO37" s="1"/>
     </row>
-    <row r="38" spans="2:41">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -3011,7 +2426,7 @@
       <c r="AN38" s="1"/>
       <c r="AO38" s="1"/>
     </row>
-    <row r="39" spans="2:41">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -3053,7 +2468,7 @@
       <c r="AN39" s="1"/>
       <c r="AO39" s="1"/>
     </row>
-    <row r="40" spans="2:41">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -3095,7 +2510,7 @@
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
     </row>
-    <row r="41" spans="2:41">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -3138,8 +2553,8 @@
       <c r="AO41" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/Dungeon0020.xlsx
+++ b/Assets/Data/Dungeon0020.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8A946A-8BBC-40E6-B5F6-44B5707BD908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DA29E0-1A1C-4916-9279-5942118A8801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="13">
   <si>
     <t>Id</t>
   </si>
@@ -485,10 +485,10 @@
         <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1210,13 +1210,9 @@
       <c r="G12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="J12" s="1"/>
       <c r="K12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1339,9 +1335,7 @@
         <v>8</v>
       </c>
       <c r="H14" s="1"/>
-      <c r="I14" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1" t="s">
         <v>8</v>

--- a/Assets/Data/Dungeon0020.xlsx
+++ b/Assets/Data/Dungeon0020.xlsx
@@ -1,38 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DA29E0-1A1C-4916-9279-5942118A8801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
     <sheet name="B1F" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="15">
   <si>
     <t>Id</t>
   </si>
@@ -58,10 +41,16 @@
     <t>InitDir</t>
   </si>
   <si>
+    <t>Completion</t>
+  </si>
+  <si>
     <t>■</t>
   </si>
   <si>
     <t>Mv</t>
+  </si>
+  <si>
+    <t>□</t>
   </si>
   <si>
     <t>Out</t>
@@ -76,8 +65,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,22 +88,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="6"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -116,9 +434,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -133,17 +693,61 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
+    <cellStyle name="入力" xfId="2" builtinId="20"/>
+    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
+    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
+    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
+    <cellStyle name="通貨" xfId="6" builtinId="4"/>
+    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
+    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
+    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="良い" xfId="13" builtinId="26"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11"/>
+    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
+    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
+    <cellStyle name="説明文" xfId="17" builtinId="53"/>
+    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
+    <cellStyle name="出力" xfId="19" builtinId="21"/>
+    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
+    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
+    <cellStyle name="計算" xfId="22" builtinId="22"/>
+    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
+    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
+    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
+    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
+    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
+    <cellStyle name="集計" xfId="28" builtinId="25"/>
+    <cellStyle name="悪い" xfId="29" builtinId="27"/>
+    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
+    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
+    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
+    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
+    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
+    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
+    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
+    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
+    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
+    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
+    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
+    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
+    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
+    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
+    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
+    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
+    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -430,16 +1034,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="1"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -464,8 +1068,11 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>20</v>
       </c>
@@ -490,28 +1097,32 @@
       <c r="H2">
         <v>3</v>
       </c>
+      <c r="I2">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AO41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="3.26953125" customWidth="1"/>
-    <col min="2" max="2" width="2.26953125" customWidth="1"/>
-    <col min="3" max="3" width="3.54296875" customWidth="1"/>
-    <col min="4" max="8" width="2.26953125" customWidth="1"/>
-    <col min="9" max="10" width="3.54296875" customWidth="1"/>
-    <col min="11" max="40" width="3.26953125" customWidth="1"/>
-    <col min="41" max="41" width="2.81640625" customWidth="1"/>
+    <col min="1" max="1" width="3.27272727272727" customWidth="1"/>
+    <col min="2" max="2" width="2.27272727272727" customWidth="1"/>
+    <col min="3" max="3" width="3.54545454545455" customWidth="1"/>
+    <col min="4" max="8" width="2.27272727272727" customWidth="1"/>
+    <col min="9" max="10" width="3.54545454545455" customWidth="1"/>
+    <col min="11" max="40" width="3.27272727272727" customWidth="1"/>
+    <col min="41" max="41" width="2.81818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17">
       <c r="A1" s="1">
         <v>0</v>
       </c>
@@ -564,44 +1175,58 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:41">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
@@ -627,40 +1252,54 @@
       <c r="AN2" s="1"/>
       <c r="AO2" s="1"/>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:41">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
@@ -686,40 +1325,54 @@
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:41">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
@@ -745,40 +1398,54 @@
       <c r="AN4" s="1"/>
       <c r="AO4" s="1"/>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
@@ -804,40 +1471,54 @@
       <c r="AN5" s="1"/>
       <c r="AO5" s="1"/>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
@@ -863,40 +1544,54 @@
       <c r="AN6" s="1"/>
       <c r="AO6" s="1"/>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
@@ -922,52 +1617,54 @@
       <c r="AN7" s="1"/>
       <c r="AO7" s="1"/>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q8" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
@@ -993,44 +1690,46 @@
       <c r="AN8" s="1"/>
       <c r="AO8" s="1"/>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q9" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
@@ -1056,46 +1755,48 @@
       <c r="AN9" s="1"/>
       <c r="AO9" s="1"/>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q10" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
@@ -1121,50 +1822,52 @@
       <c r="AN10" s="1"/>
       <c r="AO10" s="1"/>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q11" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
@@ -1190,46 +1893,48 @@
       <c r="AN11" s="1"/>
       <c r="AO11" s="1"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O12" s="1"/>
       <c r="P12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q12" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
@@ -1255,12 +1960,12 @@
       <c r="AN12" s="1"/>
       <c r="AO12" s="1"/>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -1271,22 +1976,24 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O13" s="1"/>
       <c r="P13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q13" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
@@ -1312,48 +2019,50 @@
       <c r="AN13" s="1"/>
       <c r="AO13" s="1"/>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O14" s="1"/>
       <c r="P14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
@@ -1379,17 +2088,27 @@
       <c r="AN14" s="1"/>
       <c r="AO14" s="1"/>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
+      <c r="B15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="G15" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1400,9 +2119,11 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -1428,46 +2149,58 @@
       <c r="AN15" s="1"/>
       <c r="AO15" s="1"/>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="B16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="G16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q16" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
@@ -1493,26 +2226,58 @@
       <c r="AN16" s="1"/>
       <c r="AO16" s="1"/>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:41">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
+      <c r="B17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
@@ -1538,7 +2303,7 @@
       <c r="AN17" s="1"/>
       <c r="AO17" s="1"/>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:41">
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -1580,7 +2345,7 @@
       <c r="AN18" s="1"/>
       <c r="AO18" s="1"/>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:41">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -1622,7 +2387,7 @@
       <c r="AN19" s="1"/>
       <c r="AO19" s="1"/>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:41">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -1664,7 +2429,7 @@
       <c r="AN20" s="1"/>
       <c r="AO20" s="1"/>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:41">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -1706,7 +2471,7 @@
       <c r="AN21" s="1"/>
       <c r="AO21" s="1"/>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:41">
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -1748,7 +2513,7 @@
       <c r="AN22" s="1"/>
       <c r="AO22" s="1"/>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:41">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -1790,7 +2555,7 @@
       <c r="AN23" s="1"/>
       <c r="AO23" s="1"/>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:41">
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -1832,7 +2597,7 @@
       <c r="AN24" s="1"/>
       <c r="AO24" s="1"/>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:41">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -1874,7 +2639,7 @@
       <c r="AN25" s="1"/>
       <c r="AO25" s="1"/>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:41">
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -1916,7 +2681,7 @@
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:41">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -1958,7 +2723,7 @@
       <c r="AN27" s="1"/>
       <c r="AO27" s="1"/>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:41">
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -2000,7 +2765,7 @@
       <c r="AN28" s="1"/>
       <c r="AO28" s="1"/>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:41">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -2042,7 +2807,7 @@
       <c r="AN29" s="1"/>
       <c r="AO29" s="1"/>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:41">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -2084,7 +2849,7 @@
       <c r="AN30" s="1"/>
       <c r="AO30" s="1"/>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:41">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -2126,7 +2891,7 @@
       <c r="AN31" s="1"/>
       <c r="AO31" s="1"/>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:41">
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -2168,7 +2933,7 @@
       <c r="AN32" s="1"/>
       <c r="AO32" s="1"/>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41">
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -2210,7 +2975,7 @@
       <c r="AN33" s="1"/>
       <c r="AO33" s="1"/>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41">
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -2252,7 +3017,7 @@
       <c r="AN34" s="1"/>
       <c r="AO34" s="1"/>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -2294,7 +3059,7 @@
       <c r="AN35" s="1"/>
       <c r="AO35" s="1"/>
     </row>
-    <row r="36" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:41">
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -2336,7 +3101,7 @@
       <c r="AN36" s="1"/>
       <c r="AO36" s="1"/>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41">
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -2378,7 +3143,7 @@
       <c r="AN37" s="1"/>
       <c r="AO37" s="1"/>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41">
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -2420,7 +3185,7 @@
       <c r="AN38" s="1"/>
       <c r="AO38" s="1"/>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41">
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -2462,7 +3227,7 @@
       <c r="AN39" s="1"/>
       <c r="AO39" s="1"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41">
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -2504,7 +3269,7 @@
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41">
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -2547,8 +3312,8 @@
       <c r="AO41" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/Dungeon0020.xlsx
+++ b/Assets/Data/Dungeon0020.xlsx
@@ -68,8 +68,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -88,6 +88,67 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -96,7 +157,45 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -112,60 +211,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -173,60 +219,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,7 +241,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -253,43 +277,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -307,7 +295,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -319,7 +397,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -331,97 +421,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,36 +446,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -506,15 +476,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -532,6 +493,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -540,7 +540,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -549,7 +549,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -558,127 +558,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Dungeon0020.xlsx
+++ b/Assets/Data/Dungeon0020.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
     <sheet name="B1F" sheetId="1" r:id="rId2"/>
+    <sheet name="Regeon" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="17">
   <si>
     <t>Id</t>
   </si>
@@ -61,16 +62,22 @@
   <si>
     <t>Mg</t>
   </si>
+  <si>
+    <t>②</t>
+  </si>
+  <si>
+    <t>①</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -88,11 +95,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -110,13 +130,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -125,11 +138,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -141,9 +162,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -153,21 +181,6 @@
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -186,26 +199,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -219,14 +225,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,13 +248,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -265,19 +284,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -289,13 +296,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -319,13 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -337,49 +404,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -397,31 +422,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -450,11 +457,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -476,11 +504,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -488,23 +514,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -518,17 +529,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -540,145 +547,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3316,4 +3323,857 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Q17"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="3" width="3.54545454545455" customWidth="1"/>
+    <col min="4" max="4" width="4.72727272727273" customWidth="1"/>
+    <col min="5" max="8" width="3.54545454545455" customWidth="1"/>
+    <col min="9" max="9" width="3.90909090909091" customWidth="1"/>
+    <col min="10" max="11" width="3.54545454545455" customWidth="1"/>
+    <col min="12" max="12" width="3.90909090909091" customWidth="1"/>
+    <col min="13" max="16" width="3.54545454545455" customWidth="1"/>
+    <col min="17" max="17" width="3.63636363636364" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17">
+      <c r="A1" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Assets/Data/Dungeon0020.xlsx
+++ b/Assets/Data/Dungeon0020.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="17">
   <si>
     <t>Id</t>
   </si>
@@ -48,10 +48,10 @@
     <t>■</t>
   </si>
   <si>
-    <t>Mv</t>
+    <t>□</t>
   </si>
   <si>
-    <t>□</t>
+    <t>Mv</t>
   </si>
   <si>
     <t>Out</t>
@@ -74,9 +74,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -96,14 +96,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -123,8 +116,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -132,9 +134,38 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -151,51 +182,6 @@
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -233,7 +219,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,7 +248,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -260,19 +278,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -284,7 +290,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -296,55 +308,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -362,19 +332,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +380,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,25 +398,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -457,32 +457,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -511,6 +492,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -529,13 +525,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -547,7 +547,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -556,7 +556,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -565,127 +565,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1129,7 +1129,7 @@
     <col min="41" max="41" width="2.81818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:21">
       <c r="A1" s="1">
         <v>0</v>
       </c>
@@ -1181,6 +1181,10 @@
       <c r="Q1" s="1">
         <v>16</v>
       </c>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
     </row>
     <row r="2" spans="1:41">
       <c r="A2" s="1">
@@ -1199,40 +1203,40 @@
         <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -1274,10 +1278,10 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>9</v>
@@ -1287,25 +1291,25 @@
         <v>9</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
@@ -1347,10 +1351,10 @@
         <v>9</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>9</v>
@@ -1360,25 +1364,25 @@
         <v>9</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
@@ -1417,13 +1421,13 @@
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>9</v>
@@ -1433,25 +1437,25 @@
         <v>9</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
@@ -1490,13 +1494,13 @@
         <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>9</v>
@@ -1506,25 +1510,25 @@
         <v>9</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
@@ -1563,13 +1567,13 @@
         <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>9</v>
@@ -1579,25 +1583,25 @@
         <v>9</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
@@ -1636,13 +1640,13 @@
         <v>9</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>9</v>
@@ -1670,7 +1674,7 @@
         <v>9</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
@@ -1709,13 +1713,13 @@
         <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>9</v>
@@ -1735,7 +1739,7 @@
         <v>9</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
@@ -1774,13 +1778,13 @@
         <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>9</v>
@@ -1802,7 +1806,7 @@
         <v>9</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
@@ -1841,10 +1845,10 @@
         <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>9</v>
@@ -1873,7 +1877,7 @@
         <v>9</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
@@ -1940,7 +1944,7 @@
         <v>9</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
@@ -1999,7 +2003,7 @@
         <v>9</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
@@ -2068,7 +2072,7 @@
         <v>9</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
@@ -2100,19 +2104,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>9</v>
@@ -2129,7 +2133,7 @@
         <v>9</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
@@ -2161,19 +2165,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>9</v>
@@ -2206,7 +2210,7 @@
         <v>9</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
@@ -2238,52 +2242,52 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
@@ -3328,7 +3332,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="3" width="3.54545454545455" customWidth="1"/>
@@ -3341,7 +3345,7 @@
     <col min="17" max="17" width="3.63636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:20">
       <c r="A1" s="1">
         <v>0</v>
       </c>
@@ -3393,8 +3397,13 @@
       <c r="Q1" s="1">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" s="1">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3420,34 +3429,39 @@
         <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
+        <v>10</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3475,28 +3489,33 @@
         <v>9</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
+        <v>10</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3524,28 +3543,33 @@
         <v>9</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
+        <v>10</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+    </row>
+    <row r="5" spans="1:20">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -3573,28 +3597,33 @@
         <v>9</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
+        <v>10</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+    </row>
+    <row r="6" spans="1:20">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -3622,28 +3651,33 @@
         <v>9</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17">
+        <v>10</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+    </row>
+    <row r="7" spans="1:20">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -3671,28 +3705,33 @@
         <v>9</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17">
+        <v>10</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -3738,10 +3777,15 @@
         <v>9</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17">
+        <v>10</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+    </row>
+    <row r="9" spans="1:20">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -3783,10 +3827,15 @@
         <v>9</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17">
+        <v>10</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+    </row>
+    <row r="10" spans="1:20">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -3830,10 +3879,15 @@
         <v>9</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
+        <v>10</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+    </row>
+    <row r="11" spans="1:20">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -3879,10 +3933,15 @@
         <v>9</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
+        <v>10</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -3928,10 +3987,15 @@
         <v>9</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17">
+        <v>10</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -3969,10 +4033,15 @@
         <v>9</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17">
+        <v>10</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+    </row>
+    <row r="14" spans="1:20">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -4020,27 +4089,32 @@
         <v>9</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17">
+        <v>10</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+    </row>
+    <row r="15" spans="1:20">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>9</v>
@@ -4063,27 +4137,32 @@
         <v>9</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
+        <v>10</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+    </row>
+    <row r="16" spans="1:20">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>9</v>
@@ -4116,60 +4195,80 @@
         <v>9</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
+        <v>10</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+    </row>
+    <row r="17" spans="1:20">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Dungeon0020.xlsx
+++ b/Assets/Data/Dungeon0020.xlsx
@@ -105,10 +105,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -126,9 +126,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -142,7 +165,67 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -158,31 +241,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -197,74 +263,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,7 +279,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -291,49 +429,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -345,79 +441,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -429,31 +453,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,6 +470,39 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -500,30 +533,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -534,6 +543,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -552,24 +570,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -578,145 +578,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -832,169 +832,177 @@
         </row>
         <row r="4">
           <cell r="D4">
-            <v>2010</v>
+            <v>1020</v>
           </cell>
           <cell r="E4" t="str">
-            <v>ダンジョンから出る</v>
+            <v>エンフェリアイベント再生</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2020</v>
+            <v>2010</v>
           </cell>
           <cell r="E5" t="str">
-            <v>ダンジョン移動</v>
+            <v>ダンジョンから出る</v>
           </cell>
         </row>
         <row r="6">
           <cell r="D6">
-            <v>2021</v>
+            <v>2020</v>
           </cell>
           <cell r="E6" t="str">
-            <v>移動判定なしでダンジョン移動</v>
+            <v>ダンジョン移動</v>
           </cell>
         </row>
         <row r="7">
           <cell r="D7">
-            <v>2030</v>
+            <v>2021</v>
           </cell>
           <cell r="E7" t="str">
-            <v>ダンジョンクリア</v>
+            <v>移動判定なしでダンジョン移動</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>3010</v>
+            <v>2030</v>
           </cell>
           <cell r="E8" t="str">
-            <v>アーティファクト取得</v>
+            <v>ダンジョンクリア</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>3020</v>
+            <v>3010</v>
           </cell>
           <cell r="E9" t="str">
-            <v>アイテム取得</v>
+            <v>アーティファクト取得</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>3030</v>
+            <v>3020</v>
           </cell>
           <cell r="E10" t="str">
-            <v>魔法入手</v>
+            <v>アイテム取得</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>4010</v>
+            <v>3030</v>
           </cell>
           <cell r="E11" t="str">
-            <v>仲間を増やす</v>
+            <v>魔法入手</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12">
-            <v>4011</v>
+            <v>4010</v>
           </cell>
           <cell r="E12" t="str">
-            <v>仲間を外す</v>
+            <v>仲間を増やす</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13">
-            <v>4020</v>
+            <v>4011</v>
           </cell>
           <cell r="E13" t="str">
-            <v>選択して仲間を増やす</v>
+            <v>仲間を外す</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14">
-            <v>5010</v>
+            <v>4020</v>
           </cell>
           <cell r="E14" t="str">
-            <v>強制戦闘</v>
+            <v>選択して仲間を増やす</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15">
-            <v>5020</v>
+            <v>5010</v>
           </cell>
           <cell r="E15" t="str">
-            <v>強制ボス戦闘</v>
+            <v>強制戦闘</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16">
-            <v>6010</v>
+            <v>5020</v>
           </cell>
           <cell r="E16" t="str">
-            <v>指定のイベントマスを消す</v>
+            <v>強制ボス戦闘</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17">
-            <v>6011</v>
+            <v>6010</v>
           </cell>
           <cell r="E17" t="str">
-            <v>指定のイベントマスを表示する</v>
+            <v>指定のイベントマスを消す</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18">
-            <v>6020</v>
+            <v>6011</v>
           </cell>
           <cell r="E18" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+            <v>指定のイベントマスを表示する</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19">
-            <v>6030</v>
+            <v>6020</v>
           </cell>
           <cell r="E19" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>7010</v>
+            <v>6030</v>
           </cell>
           <cell r="E20" t="str">
-            <v>ダメージ床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21">
-            <v>7020</v>
+            <v>7010</v>
           </cell>
           <cell r="E21" t="str">
-            <v>怨嗟床</v>
+            <v>ダメージ床</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22">
-            <v>7021</v>
+            <v>7020</v>
           </cell>
           <cell r="E22" t="str">
-            <v>怨嗟床解除</v>
+            <v>怨嗟床</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23">
-            <v>8010</v>
+            <v>7021</v>
           </cell>
           <cell r="E23" t="str">
-            <v>指定リージョンを開示する</v>
+            <v>怨嗟床解除</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24">
+            <v>8010</v>
+          </cell>
+          <cell r="E24" t="str">
+            <v>指定リージョンを開示する</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="D25">
             <v>9010</v>
           </cell>
-          <cell r="E24" t="str">
+          <cell r="E25" t="str">
             <v>イベント終了明示</v>
           </cell>
         </row>
@@ -4524,8 +4532,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
+  <cols>
+    <col min="7" max="7" width="24.6363636363636" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
@@ -4704,23 +4715,23 @@
         <v>3010</v>
       </c>
       <c r="F6">
-        <v>9010</v>
+        <v>1020</v>
       </c>
       <c r="G6" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F6,[1]Define!D:D))</f>
-        <v>イベント終了明示</v>
+        <v>エンフェリアイベント再生</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -4728,32 +4739,32 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <v>3010</v>
       </c>
       <c r="F7">
-        <v>2020</v>
+        <v>9010</v>
       </c>
       <c r="G7" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F7,[1]Define!D:D))</f>
-        <v>ダンジョン移動</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H7">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="b">
         <v>1</v>
-      </c>
-      <c r="J7">
-        <v>15</v>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -4761,29 +4772,29 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>3010</v>
       </c>
       <c r="F8">
-        <v>8010</v>
+        <v>2020</v>
       </c>
       <c r="G8" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F8,[1]Define!D:D))</f>
-        <v>指定リージョンを開示する</v>
+        <v>ダンジョン移動</v>
       </c>
       <c r="H8">
+        <v>21</v>
+      </c>
+      <c r="I8">
         <v>1</v>
       </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
       <c r="J8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -4794,10 +4805,10 @@
         <v>20</v>
       </c>
       <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9">
         <v>11</v>
-      </c>
-      <c r="C9">
-        <v>7</v>
       </c>
       <c r="D9">
         <v>3010</v>
@@ -4810,7 +4821,7 @@
         <v>指定リージョンを開示する</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -4819,7 +4830,40 @@
         <v>0</v>
       </c>
       <c r="K9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>20</v>
+      </c>
+      <c r="B10">
+        <v>11</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+      <c r="D10">
+        <v>3010</v>
+      </c>
+      <c r="F10">
+        <v>8010</v>
+      </c>
+      <c r="G10" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F10,[1]Define!D:D))</f>
+        <v>指定リージョンを開示する</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10">
         <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Dungeon0020.xlsx
+++ b/Assets/Data/Dungeon0020.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -105,9 +105,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -126,77 +126,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -211,21 +142,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,6 +151,22 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,7 +181,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,9 +195,76 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,7 +279,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -291,25 +417,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -327,73 +447,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -405,61 +459,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,30 +470,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -547,11 +523,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -570,6 +552,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -578,145 +578,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -739,12 +739,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>

--- a/Assets/Data/Dungeon0020.xlsx
+++ b/Assets/Data/Dungeon0020.xlsx
@@ -126,6 +126,59 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -148,9 +201,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -164,9 +216,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -180,13 +231,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -195,15 +239,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -211,7 +248,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -226,45 +263,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,25 +279,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -309,25 +297,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -339,37 +309,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,7 +327,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,19 +351,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -423,7 +369,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,13 +441,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,13 +459,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,15 +470,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -499,11 +490,44 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -519,21 +543,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -561,15 +570,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -578,7 +578,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -587,136 +587,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
